--- a/preds_oro_garch.xlsx
+++ b/preds_oro_garch.xlsx
@@ -433,7 +433,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>101.7767360873029</v>
+        <v>107.2787120886027</v>
       </c>
     </row>
     <row r="3">
@@ -441,7 +441,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>103.7929563423226</v>
+        <v>109.0960132952931</v>
       </c>
     </row>
     <row r="4">
@@ -449,7 +449,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>105.7707500397632</v>
+        <v>110.8835342441077</v>
       </c>
     </row>
     <row r="5">
@@ -457,7 +457,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>107.7122339461439</v>
+        <v>112.6426926879932</v>
       </c>
     </row>
     <row r="6">
@@ -465,7 +465,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>109.6193373422939</v>
+        <v>114.3747973355106</v>
       </c>
     </row>
   </sheetData>
